--- a/Project/01. CYGNET/01. Payment Block/Desktop Files/Daily Working/Working_2.xlsx
+++ b/Project/01. CYGNET/01. Payment Block/Desktop Files/Daily Working/Working_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Others\Daily Working\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05. Daily (21-Mar-26) - 6GB\VSCode\Project\01. CYGNET\01. Payment Block\Desktop Files\Daily Working\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0339E9E-704C-44BA-8DE8-A081E0640060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{901B352B-4B00-46EE-90BB-82687C75ED31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="831" firstSheet="1" activeTab="3" xr2:uid="{9C1480C7-C5E0-4C42-9747-CF76F95A8F8D}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="1416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="1425">
   <si>
     <r>
       <t>REPORT</t>
@@ -26921,6 +26921,232 @@
         <family val="3"/>
       </rPr>
       <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>IF TRUE-&gt;</t>
+  </si>
+  <si>
+    <t>PRONLY</t>
+  </si>
+  <si>
+    <t>MATCHEDBYTOLERANCE,  NEARMATCHED</t>
+  </si>
+  <si>
+    <t>R &amp; I</t>
+  </si>
+  <si>
+    <r>
+      <t>BEGIN OF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> mcs_reco_status_cat,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        matched   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF222E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> TYPE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> zcy_t_2a_recstat-category </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF222E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>VALUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0A3069"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'M'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        mismatched</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF222E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> TYPE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> zcy_t_2a_recstat-category </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF222E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>VALUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0A3069"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'B'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        exempted  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF222E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> TYPE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> zcy_t_2a_recstat-category </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF222E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>VALUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0A3069"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'X'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCF222E"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>END OF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> mcs_reco_status_cat,</t>
     </r>
   </si>
 </sst>
@@ -27427,7 +27653,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -27568,17 +27794,41 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -27598,43 +27848,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -28857,14 +29089,14 @@
     </row>
     <row r="67" spans="3:10" ht="15.75" thickBot="1"/>
     <row r="68" spans="3:10">
-      <c r="E68" s="76" t="s">
+      <c r="E68" s="97" t="s">
         <v>753</v>
       </c>
-      <c r="F68" s="77"/>
-      <c r="G68" s="77"/>
-      <c r="H68" s="77"/>
-      <c r="I68" s="77"/>
-      <c r="J68" s="78"/>
+      <c r="F68" s="98"/>
+      <c r="G68" s="98"/>
+      <c r="H68" s="98"/>
+      <c r="I68" s="98"/>
+      <c r="J68" s="99"/>
     </row>
     <row r="69" spans="3:10">
       <c r="E69" s="51" t="s">
@@ -36033,7 +36265,7 @@
     <col min="23" max="23" width="37.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="20:21">
+    <row r="2" spans="18:21">
       <c r="T2" t="s">
         <v>21</v>
       </c>
@@ -36041,65 +36273,117 @@
         <v>21</v>
       </c>
     </row>
+    <row r="14" spans="18:21">
+      <c r="R14" t="s">
+        <v>80</v>
+      </c>
+      <c r="T14" t="s">
+        <v>74</v>
+      </c>
+      <c r="U14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="18:21">
+      <c r="R15" t="s">
+        <v>80</v>
+      </c>
+      <c r="T15" t="s">
+        <v>68</v>
+      </c>
+      <c r="U15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="18:21">
+      <c r="R16" t="s">
+        <v>80</v>
+      </c>
+      <c r="T16" t="s">
+        <v>52</v>
+      </c>
+      <c r="U16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="18:24">
+      <c r="R17" t="s">
+        <v>80</v>
+      </c>
+      <c r="T17" t="s">
+        <v>72</v>
+      </c>
+      <c r="U17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="18:24">
+      <c r="R18" t="s">
+        <v>80</v>
+      </c>
+      <c r="T18" t="s">
+        <v>60</v>
+      </c>
+      <c r="U18" t="s">
+        <v>61</v>
+      </c>
+    </row>
     <row r="19" spans="18:24">
+      <c r="R19" t="s">
+        <v>80</v>
+      </c>
       <c r="T19" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="U19" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="18:24">
+      <c r="R20" t="s">
+        <v>80</v>
+      </c>
+      <c r="T20" t="s">
+        <v>54</v>
+      </c>
+      <c r="U20" t="s">
+        <v>55</v>
+      </c>
       <c r="X20" s="3"/>
     </row>
     <row r="21" spans="18:24">
+      <c r="R21" t="s">
+        <v>80</v>
+      </c>
       <c r="T21" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="U21" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="X21" s="3"/>
     </row>
     <row r="22" spans="18:24">
+      <c r="R22" t="s">
+        <v>80</v>
+      </c>
       <c r="T22" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="U22" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="X22" s="3"/>
     </row>
     <row r="23" spans="18:24">
+      <c r="R23" t="s">
+        <v>80</v>
+      </c>
       <c r="T23" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="U23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="18:24">
-      <c r="T24" t="s">
-        <v>58</v>
-      </c>
-      <c r="U24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="18:24">
-      <c r="T25" t="s">
-        <v>60</v>
-      </c>
-      <c r="U25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="18:24">
-      <c r="T26" t="s">
-        <v>62</v>
-      </c>
-      <c r="U26" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="18:24">
@@ -36121,57 +36405,24 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="18:24">
-      <c r="R29" t="s">
-        <v>80</v>
-      </c>
-      <c r="T29" t="s">
-        <v>68</v>
-      </c>
-      <c r="U29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="18:24">
-      <c r="R30" t="s">
-        <v>80</v>
-      </c>
-      <c r="T30" t="s">
-        <v>70</v>
-      </c>
-      <c r="U30" t="s">
-        <v>71</v>
-      </c>
-    </row>
     <row r="31" spans="18:24">
       <c r="T31" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="U31" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="18:24">
-      <c r="R32" t="s">
-        <v>80</v>
-      </c>
-      <c r="T32" t="s">
-        <v>74</v>
-      </c>
-      <c r="U32" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="18:23" ht="15.75" thickBot="1"/>
     <row r="34" spans="18:23">
-      <c r="R34" s="76" t="s">
+      <c r="R34" s="97" t="s">
         <v>753</v>
       </c>
-      <c r="S34" s="77"/>
-      <c r="T34" s="77"/>
-      <c r="U34" s="77"/>
-      <c r="V34" s="77"/>
-      <c r="W34" s="78"/>
+      <c r="S34" s="98"/>
+      <c r="T34" s="98"/>
+      <c r="U34" s="98"/>
+      <c r="V34" s="98"/>
+      <c r="W34" s="99"/>
     </row>
     <row r="35" spans="18:23">
       <c r="R35" s="51" t="s">
@@ -36454,7 +36705,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B81B9D2-BD9A-4254-8D30-C6D323F9A995}">
-  <dimension ref="C4:M34"/>
+  <dimension ref="C4:M41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="21.28515625" customWidth="1"/>
@@ -36471,39 +36722,39 @@
       </c>
     </row>
     <row r="6" spans="3:13">
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="88" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="84"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="90"/>
     </row>
     <row r="7" spans="3:13">
-      <c r="D7" s="82" t="s">
+      <c r="D7" s="88" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="83"/>
+      <c r="E7" s="89"/>
       <c r="F7" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="85" t="s">
+      <c r="G7" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="87"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="93"/>
     </row>
     <row r="8" spans="3:13">
-      <c r="D8" s="88" t="s">
+      <c r="D8" s="83" t="s">
         <v>84</v>
       </c>
       <c r="E8" s="7" t="s">
@@ -36512,50 +36763,50 @@
       <c r="F8" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="G8" s="91" t="s">
+      <c r="G8" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="92"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="92"/>
-      <c r="K8" s="92"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="93"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="78"/>
     </row>
     <row r="9" spans="3:13">
-      <c r="D9" s="89"/>
+      <c r="D9" s="94"/>
       <c r="E9" s="1" t="s">
         <v>86</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="G9" s="94"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="95"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="95"/>
-      <c r="M9" s="96"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="80"/>
+      <c r="M9" s="81"/>
     </row>
     <row r="10" spans="3:13">
-      <c r="D10" s="90"/>
+      <c r="D10" s="84"/>
       <c r="E10" s="10" t="s">
         <v>87</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G10" s="94"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="95"/>
-      <c r="M10" s="96"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="80"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="80"/>
+      <c r="L10" s="80"/>
+      <c r="M10" s="81"/>
     </row>
     <row r="11" spans="3:13">
-      <c r="D11" s="88" t="s">
+      <c r="D11" s="83" t="s">
         <v>88</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -36564,34 +36815,34 @@
       <c r="F11" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="91" t="s">
+      <c r="G11" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="92"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="92"/>
-      <c r="K11" s="92"/>
-      <c r="L11" s="92"/>
-      <c r="M11" s="93"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="78"/>
     </row>
     <row r="12" spans="3:13">
-      <c r="D12" s="90"/>
+      <c r="D12" s="84"/>
       <c r="E12" s="14" t="s">
         <v>90</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="G12" s="94"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="95"/>
-      <c r="K12" s="95"/>
-      <c r="L12" s="95"/>
-      <c r="M12" s="96"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="80"/>
+      <c r="L12" s="80"/>
+      <c r="M12" s="81"/>
     </row>
     <row r="13" spans="3:13">
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="83" t="s">
         <v>91</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -36600,31 +36851,31 @@
       <c r="F13" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="91" t="s">
+      <c r="G13" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="92"/>
-      <c r="I13" s="92"/>
-      <c r="J13" s="92"/>
-      <c r="K13" s="92"/>
-      <c r="L13" s="92"/>
-      <c r="M13" s="93"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
+      <c r="M13" s="78"/>
     </row>
     <row r="14" spans="3:13">
-      <c r="D14" s="90"/>
+      <c r="D14" s="84"/>
       <c r="E14" s="14" t="s">
         <v>90</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="97"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="99"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="86"/>
+      <c r="M14" s="87"/>
     </row>
     <row r="17" spans="3:12">
       <c r="C17">
@@ -36704,93 +36955,107 @@
       <c r="D29" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="80" t="s">
+      <c r="F29" s="95" t="s">
         <v>112</v>
       </c>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
-      <c r="J29" s="80" t="s">
+      <c r="G29" s="95"/>
+      <c r="H29" s="95"/>
+      <c r="J29" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="K29" s="80"/>
-      <c r="L29" s="80"/>
+      <c r="K29" s="95"/>
+      <c r="L29" s="95"/>
     </row>
     <row r="30" spans="3:12">
       <c r="D30" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="81" t="s">
+      <c r="F30" s="96" t="s">
         <v>111</v>
       </c>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="J30" s="81" t="s">
+      <c r="G30" s="96"/>
+      <c r="H30" s="96"/>
+      <c r="J30" s="96" t="s">
         <v>111</v>
       </c>
-      <c r="K30" s="81"/>
-      <c r="L30" s="81"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="96"/>
     </row>
     <row r="31" spans="3:12">
       <c r="D31" t="s">
         <v>109</v>
       </c>
-      <c r="F31" s="79" t="s">
+      <c r="F31" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
-      <c r="J31" s="79" t="s">
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+      <c r="J31" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="K31" s="79"/>
-      <c r="L31" s="79"/>
+      <c r="K31" s="82"/>
+      <c r="L31" s="82"/>
     </row>
     <row r="32" spans="3:12">
       <c r="D32" t="s">
         <v>110</v>
       </c>
-      <c r="F32" s="79" t="s">
+      <c r="F32" s="82" t="s">
         <v>117</v>
       </c>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
-      <c r="J32" s="79"/>
-      <c r="K32" s="79"/>
-      <c r="L32" s="79"/>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+      <c r="J32" s="82"/>
+      <c r="K32" s="82"/>
+      <c r="L32" s="82"/>
     </row>
     <row r="33" spans="6:12">
-      <c r="F33" s="79" t="s">
+      <c r="F33" s="82" t="s">
         <v>118</v>
       </c>
-      <c r="G33" s="79"/>
-      <c r="H33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="J33" s="82"/>
+      <c r="K33" s="82"/>
+      <c r="L33" s="82"/>
     </row>
     <row r="34" spans="6:12">
-      <c r="F34" s="79" t="s">
+      <c r="F34" s="82" t="s">
         <v>119</v>
       </c>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="79"/>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+      <c r="J34" s="82"/>
+      <c r="K34" s="82"/>
+      <c r="L34" s="82"/>
+    </row>
+    <row r="37" spans="6:12">
+      <c r="J37" s="1" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="38" spans="6:12">
+      <c r="J38" s="3" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="39" spans="6:12">
+      <c r="J39" s="3" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="40" spans="6:12">
+      <c r="J40" s="3" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="41" spans="6:12">
+      <c r="J41" s="3" t="s">
+        <v>1424</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="G11:M12"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="G13:M14"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="G7:M7"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="G8:M10"/>
     <mergeCell ref="F34:H34"/>
     <mergeCell ref="J29:L29"/>
     <mergeCell ref="J30:L30"/>
@@ -36801,6 +37066,17 @@
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F31:H31"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="G7:M7"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="G8:M10"/>
+    <mergeCell ref="G11:M12"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="G13:M14"/>
+    <mergeCell ref="D11:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -36809,7 +37085,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2DE603F-8A2D-4C7F-97A1-E0196E04BDF2}">
-  <dimension ref="A4:W40"/>
+  <dimension ref="A4:W48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="19" max="19" width="9.85546875" customWidth="1"/>
@@ -36988,7 +37264,7 @@
       </c>
       <c r="W16" s="16"/>
     </row>
-    <row r="17" spans="2:23" ht="15.75" thickBot="1">
+    <row r="17" spans="3:23" ht="15.75" thickBot="1">
       <c r="K17" s="24" t="s">
         <v>146</v>
       </c>
@@ -36998,7 +37274,7 @@
       </c>
       <c r="W17" s="16"/>
     </row>
-    <row r="18" spans="2:23">
+    <row r="18" spans="3:23">
       <c r="C18" s="27" t="s">
         <v>156</v>
       </c>
@@ -37016,7 +37292,7 @@
       </c>
       <c r="W18" s="16"/>
     </row>
-    <row r="19" spans="2:23">
+    <row r="19" spans="3:23">
       <c r="C19" s="30" t="s">
         <v>157</v>
       </c>
@@ -37027,7 +37303,7 @@
       </c>
       <c r="W19" s="16"/>
     </row>
-    <row r="20" spans="2:23">
+    <row r="20" spans="3:23">
       <c r="C20" s="30" t="s">
         <v>158</v>
       </c>
@@ -37040,85 +37316,184 @@
       <c r="V20" s="26"/>
       <c r="W20" s="15"/>
     </row>
-    <row r="21" spans="2:23" ht="15.75" thickBot="1">
+    <row r="21" spans="3:23" ht="15.75" thickBot="1">
       <c r="C21" s="33" t="s">
         <v>142</v>
       </c>
       <c r="D21" s="34"/>
       <c r="E21" s="35"/>
     </row>
-    <row r="25" spans="2:23">
-      <c r="B25" t="s">
+    <row r="23" spans="3:23">
+      <c r="C23" s="101">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="82" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="82"/>
+      <c r="G23" s="102" t="s">
+        <v>1416</v>
+      </c>
+      <c r="I23" t="s">
+        <v>748</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23">
+      <c r="C24" s="101">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="82" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="82"/>
+      <c r="G24" s="102"/>
+      <c r="I24" t="s">
+        <v>1417</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23">
+      <c r="C25" s="101">
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="82"/>
+      <c r="G25" s="102"/>
+      <c r="I25" t="s">
+        <v>1418</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23">
+      <c r="C26" s="101">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="82"/>
+      <c r="G26" s="102"/>
+      <c r="I26" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23">
+      <c r="C27" s="101">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="82" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="82"/>
+      <c r="G27" s="102"/>
+      <c r="I27" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" t="s">
         <v>159</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C33" t="s">
         <v>162</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D33" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="27" spans="2:23">
-      <c r="D27" t="s">
+    <row r="35" spans="2:4">
+      <c r="D35" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="28" spans="2:23">
-      <c r="D28" s="3" t="s">
+    <row r="36" spans="2:4">
+      <c r="D36" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="30" spans="2:23">
-      <c r="C30" t="s">
+    <row r="38" spans="2:4">
+      <c r="C38" t="s">
         <v>163</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D38" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="32" spans="2:23">
-      <c r="D32" t="s">
+    <row r="40" spans="2:4">
+      <c r="D40" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
-      <c r="D33" s="3" t="s">
+    <row r="41" spans="2:4">
+      <c r="D41" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
-      <c r="B35" t="s">
+    <row r="43" spans="2:4">
+      <c r="B43" t="s">
         <v>167</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C43" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
-      <c r="B36" t="s">
+    <row r="44" spans="2:4">
+      <c r="B44" t="s">
         <v>169</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C44" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
-      <c r="B37" t="s">
+    <row r="45" spans="2:4">
+      <c r="B45" t="s">
         <v>171</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C45" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="40" spans="2:4">
-      <c r="B40" t="s">
+    <row r="48" spans="2:4">
+      <c r="B48" t="s">
         <v>173</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C48" t="s">
         <v>174</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G23:G27"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
